--- a/Daily Sales Forecasting Methodology/Iteration 3/Festive_Dates.xlsx
+++ b/Daily Sales Forecasting Methodology/Iteration 3/Festive_Dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a1c0b903b3414e4/Desktop/Learning - post job/Time Series Forecasting/TFT - Study/Daily Sales Forecasting Methodology/Iteration 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A689F989-1608-40A6-8B2E-0572ECD438B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{A689F989-1608-40A6-8B2E-0572ECD438B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81CE5238-D9D7-48A2-9183-5C140CA5388A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CE69B548-6EBB-4427-8150-BF6170E86BE5}"/>
   </bookViews>
@@ -127,12 +127,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2922F5-D3FE-4130-9511-F59F0C66E5A9}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.08984375" bestFit="1" customWidth="1"/>
@@ -456,12 +457,13 @@
     <col min="4" max="4" width="17.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.08984375" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -480,17 +482,18 @@
       <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="3"/>
+      <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>2023</v>
       </c>
@@ -511,19 +514,23 @@
       <c r="F2" s="2">
         <v>45222</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="5">
+        <f>F2-E2</f>
+        <v>8</v>
+      </c>
+      <c r="H2" s="2">
         <v>45240</v>
       </c>
-      <c r="H2" s="2">
-        <f>G2+2</f>
+      <c r="I2" s="2">
+        <f>H2+2</f>
         <v>45242</v>
       </c>
-      <c r="I2" s="2">
-        <f>H2+30</f>
+      <c r="J2" s="2">
+        <f>I2+30</f>
         <v>45272</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>2024</v>
       </c>
@@ -544,19 +551,23 @@
       <c r="F3" s="2">
         <v>45577</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="5">
+        <f t="shared" ref="G3:G5" si="2">F3-E3</f>
+        <v>9</v>
+      </c>
+      <c r="H3" s="2">
         <v>45594</v>
       </c>
-      <c r="H3" s="2">
-        <f t="shared" ref="H3:H5" si="2">G3+2</f>
+      <c r="I3" s="2">
+        <f t="shared" ref="I3:I5" si="3">H3+2</f>
         <v>45596</v>
       </c>
-      <c r="I3" s="2">
-        <f t="shared" ref="I3:I5" si="3">H3+30</f>
+      <c r="J3" s="2">
+        <f t="shared" ref="J3:J5" si="4">I3+30</f>
         <v>45626</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>2025</v>
       </c>
@@ -577,19 +588,23 @@
       <c r="F4" s="2">
         <v>45931</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="5">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="H4" s="2">
         <v>45948</v>
-      </c>
-      <c r="H4" s="2">
-        <f t="shared" si="2"/>
-        <v>45950</v>
       </c>
       <c r="I4" s="2">
         <f t="shared" si="3"/>
+        <v>45950</v>
+      </c>
+      <c r="J4" s="2">
+        <f t="shared" si="4"/>
         <v>45980</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>2026</v>
       </c>
@@ -610,15 +625,19 @@
       <c r="F5" s="2">
         <v>46314</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="5">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="H5" s="2">
         <v>46332</v>
-      </c>
-      <c r="H5" s="2">
-        <f t="shared" si="2"/>
-        <v>46334</v>
       </c>
       <c r="I5" s="2">
         <f t="shared" si="3"/>
+        <v>46334</v>
+      </c>
+      <c r="J5" s="2">
+        <f t="shared" si="4"/>
         <v>46364</v>
       </c>
     </row>
